--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -443,7 +443,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -670,17 +670,39 @@
       <c r="J3" t="n">
         <v>34.87900161743164</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:09:29</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>24.8370403</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67.03366149999999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>18.54299926757812</v>
+      </c>
+      <c r="O3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>00:00:21</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0058</v>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -636,20 +636,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C3" t="n">
+        <v>3645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>114723</t>
-        </is>
+      <c r="E3" t="n">
+        <v>114723</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -668,7 +664,7 @@
         <v>67.0336556</v>
       </c>
       <c r="J3" t="n">
-        <v>34.87900161743164</v>
+        <v>34.87900162</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -682,7 +678,7 @@
         <v>67.03366149999999</v>
       </c>
       <c r="N3" t="n">
-        <v>18.54299926757812</v>
+        <v>18.54299927</v>
       </c>
       <c r="O3" t="n">
         <v>17.2</v>
@@ -694,7 +690,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>00:00:21</t>
+          <t>0:00:21</t>
         </is>
       </c>
       <c r="R3" t="n">

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -702,8 +702,67 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VIS-20260911181922-3774B9</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Zubair</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>101722</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AB Ghazi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:19:22</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>24.8370814</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.0337494</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.26599979400635</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S3"/>
+  <autoFilter ref="A1:S4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -713,20 +713,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2626</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Zubair</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>101722</t>
-        </is>
+      <c r="E4" t="n">
+        <v>101722</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -745,19 +741,41 @@
         <v>67.0337494</v>
       </c>
       <c r="J4" t="n">
-        <v>15.26599979400635</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+        <v>15.26599979</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:20:00</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>24.8370666</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67.0337605</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15.46599960327148</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>00:00:38</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0106</v>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,15 +427,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -443,7 +443,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -755,7 +755,7 @@
         <v>67.0337605</v>
       </c>
       <c r="N4" t="n">
-        <v>15.46599960327148</v>
+        <v>15.4659996</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>00:00:38</t>
+          <t>0:00:38</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -779,8 +779,67 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VIS-20260911182622-1FD4F8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Adnan Afzaal Siddiqui</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11100</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cliff Petroleum</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:26:22</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>24.837201</v>
+      </c>
+      <c r="I5" t="n">
+        <v>67.03361339999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -443,7 +443,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -790,20 +790,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4970</t>
-        </is>
+      <c r="C5" t="n">
+        <v>4970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Adnan Afzaal Siddiqui</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>11100</t>
-        </is>
+      <c r="E5" t="n">
+        <v>11100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -824,17 +820,39 @@
       <c r="J5" t="n">
         <v>100</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:26:55</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>24.8370897</v>
+      </c>
+      <c r="M5" t="n">
+        <v>67.0337269</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28.38899993896484</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>00:00:33</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0092</v>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -832,7 +832,7 @@
         <v>67.0337269</v>
       </c>
       <c r="N5" t="n">
-        <v>28.38899993896484</v>
+        <v>28.38899994</v>
       </c>
       <c r="O5" t="n">
         <v>16.9</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>00:00:33</t>
+          <t>0:00:33</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -856,8 +856,67 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VIS-20260911185514-E6AC37</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>101694</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mughal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:55:14</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>24.8370499</v>
+      </c>
+      <c r="I6" t="n">
+        <v>67.0336317</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25.79899978637695</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -867,20 +867,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C6" t="n">
+        <v>3645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>101694</t>
-        </is>
+      <c r="E6" t="n">
+        <v>101694</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -899,19 +895,41 @@
         <v>67.0336317</v>
       </c>
       <c r="J6" t="n">
-        <v>25.79899978637695</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+        <v>25.79899979</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:59:26</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>24.8370494</v>
+      </c>
+      <c r="M6" t="n">
+        <v>67.03362559999999</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26.32399940490723</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>00:04:12</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -909,7 +909,7 @@
         <v>67.03362559999999</v>
       </c>
       <c r="N6" t="n">
-        <v>26.32399940490723</v>
+        <v>26.3239994</v>
       </c>
       <c r="O6" t="n">
         <v>0.6</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>00:04:12</t>
+          <t>0:04:12</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -933,8 +933,67 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VIS-20260911190105-890E16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>101598</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mughal</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:01:05</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>24.8370181</v>
+      </c>
+      <c r="I7" t="n">
+        <v>67.0336417</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23.59600067138672</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -944,20 +944,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C7" t="n">
+        <v>3645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>101598</t>
-        </is>
+      <c r="E7" t="n">
+        <v>101598</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -976,7 +972,7 @@
         <v>67.0336417</v>
       </c>
       <c r="J7" t="n">
-        <v>23.59600067138672</v>
+        <v>23.59600067</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -992,8 +988,67 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VIS-20260911191034-095A03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Muhammad Safeer</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>102404</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>G.N PS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:10:34</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>24.8370164</v>
+      </c>
+      <c r="I8" t="n">
+        <v>67.0336535</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10.67000007629395</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -443,7 +443,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -1033,17 +1033,39 @@
       <c r="J8" t="n">
         <v>10.67000007629395</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:10:57</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>24.8370227</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67.0336497</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.60400009155273</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>00:00:23</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0064</v>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -439,13 +439,13 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -974,17 +974,39 @@
       <c r="J7" t="n">
         <v>23.59600067</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:46</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>24.9783517</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67.186215</v>
+      </c>
+      <c r="N7" t="n">
+        <v>77.88300323486328</v>
+      </c>
+      <c r="O7" t="n">
+        <v>21994.3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Big Difference</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>03:29:41</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>3.4947</v>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -999,20 +1021,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3949</t>
-        </is>
+      <c r="C8" t="n">
+        <v>3949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Muhammad Safeer</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>102404</t>
-        </is>
+      <c r="E8" t="n">
+        <v>102404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1031,7 +1049,7 @@
         <v>67.0336535</v>
       </c>
       <c r="J8" t="n">
-        <v>10.67000007629395</v>
+        <v>10.67000008</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1045,7 +1063,7 @@
         <v>67.0336497</v>
       </c>
       <c r="N8" t="n">
-        <v>10.60400009155273</v>
+        <v>10.60400009</v>
       </c>
       <c r="O8" t="n">
         <v>0.8</v>
@@ -1057,7 +1075,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>00:00:23</t>
+          <t>0:00:23</t>
         </is>
       </c>
       <c r="R8" t="n">

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -986,7 +986,7 @@
         <v>67.186215</v>
       </c>
       <c r="N7" t="n">
-        <v>77.88300323486328</v>
+        <v>77.88300323</v>
       </c>
       <c r="O7" t="n">
         <v>21994.3</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>03:29:41</t>
+          <t>3:29:41</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1087,8 +1087,67 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VIS-20260911223201-2D3EF4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>101694</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mughal</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:32:01</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>24.9772783</v>
+      </c>
+      <c r="I9" t="n">
+        <v>67.1856267</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.100000381469727</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -1098,20 +1098,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C9" t="n">
+        <v>3645</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>101694</t>
-        </is>
+      <c r="E9" t="n">
+        <v>101694</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1130,19 +1126,41 @@
         <v>67.1856267</v>
       </c>
       <c r="J9" t="n">
-        <v>8.100000381469727</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+        <v>8.100000380999999</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:32:55</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>24.9772783</v>
+      </c>
+      <c r="M9" t="n">
+        <v>67.1856267</v>
+      </c>
+      <c r="N9" t="n">
+        <v>91.81300354003906</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>00:00:54</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.015</v>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -1140,7 +1140,7 @@
         <v>67.1856267</v>
       </c>
       <c r="N9" t="n">
-        <v>91.81300354003906</v>
+        <v>91.81300354</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>00:00:54</t>
+          <t>0:00:54</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -1164,8 +1164,67 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VIS-20260911223354-C92EB8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>114723</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:33:54</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>24.978415</v>
+      </c>
+      <c r="I10" t="n">
+        <v>67.1862733</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.39999961853027</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S9"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -439,7 +439,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -1175,20 +1175,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C10" t="n">
+        <v>3645</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>114723</t>
-        </is>
+      <c r="E10" t="n">
+        <v>114723</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1207,19 +1203,41 @@
         <v>67.1862733</v>
       </c>
       <c r="J10" t="n">
-        <v>14.39999961853027</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+        <v>14.39999962</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:36:25</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>24.978734</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67.1863724</v>
+      </c>
+      <c r="N10" t="n">
+        <v>68.40000152587891</v>
+      </c>
+      <c r="O10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>00:02:31</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0419</v>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -1217,7 +1217,7 @@
         <v>67.1863724</v>
       </c>
       <c r="N10" t="n">
-        <v>68.40000152587891</v>
+        <v>68.40000153</v>
       </c>
       <c r="O10" t="n">
         <v>36.9</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>00:02:31</t>
+          <t>0:02:31</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1241,8 +1241,67 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VIS-20260911235107-3BDE7E</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>114723</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-11 23:51:07</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>24.9787332</v>
+      </c>
+      <c r="I11" t="n">
+        <v>67.1863714</v>
+      </c>
+      <c r="J11" t="n">
+        <v>77.59999847412109</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-11.xlsx
+++ b/data/visits/Visits_2026-09-11.xlsx
@@ -439,13 +439,13 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -1252,20 +1252,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C11" t="n">
+        <v>3645</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>114723</t>
-        </is>
+      <c r="E11" t="n">
+        <v>114723</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1284,19 +1280,41 @@
         <v>67.1863714</v>
       </c>
       <c r="J11" t="n">
-        <v>77.59999847412109</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+        <v>77.59999847</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-11 23:51:42</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>24.9777633</v>
+      </c>
+      <c r="M11" t="n">
+        <v>67.18591670000001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10.30000019073486</v>
+      </c>
+      <c r="O11" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Some Difference</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>00:00:35</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.0097</v>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
